--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-04-2026.xlsx
@@ -1115,7 +1115,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£27.62</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£49.11</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2771,34 +2771,34 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>£96.25</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>£60.74</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>£51.27</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>£68.22</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
           <t>POA</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>£60.74</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>£51.27</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>£68.22</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>POA</t>
-        </is>
-      </c>
       <c r="O26" t="inlineStr">
         <is>
           <t>£53.30</t>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>£48.37</t>
+          <t>£49.64</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
